--- a/dados/Informakon/contr-2025_09_23.xlsx
+++ b/dados/Informakon/contr-2025_09_23.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://incorporadoraampla.sharepoint.com/sites/Controladoria/Documentos Compartilhados/amplaGitHub/dados/Informakon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{8448E53F-4CE5-47C5-89FE-AA7471990304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{712DEFC3-E386-4695-8032-7F76F71F2AD7}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{8448E53F-4CE5-47C5-89FE-AA7471990304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5325FA72-334C-430F-913A-6D1D76FCB6DF}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1305" windowWidth="29040" windowHeight="15840" xr2:uid="{29DEE912-5D15-4CB5-8FA1-963AC2147319}"/>
+    <workbookView xWindow="-28920" yWindow="-7905" windowWidth="29040" windowHeight="15840" xr2:uid="{29DEE912-5D15-4CB5-8FA1-963AC2147319}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -12606,18 +12606,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7FF77DEF-69A7-4A59-BCA2-CE1D51CB0CEA}" name="Tabela1" displayName="Tabela1" ref="B1:AB946" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="B1:AB946" xr:uid="{7FF77DEF-69A7-4A59-BCA2-CE1D51CB0CEA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="0029-0"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="9">
-      <filters>
-        <filter val="UP JARDIM PRUDÊNCIA : 1006."/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:AB946" xr:uid="{7FF77DEF-69A7-4A59-BCA2-CE1D51CB0CEA}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{DBC07D07-5610-4B5E-ACAA-A17F8ECC9012}" name="Nº Contrato" dataCellStyle="Normal 2"/>
     <tableColumn id="2" xr3:uid="{7FEF5D8D-EF82-4669-A6B2-19229FA15F42}" name="Nº Con. Alternativo" dataCellStyle="Normal 2"/>
@@ -13080,7 +13069,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="2" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4130</v>
       </c>
@@ -13148,7 +13137,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="3" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1441</v>
       </c>
@@ -13213,7 +13202,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="4" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1441</v>
       </c>
@@ -13278,7 +13267,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="5" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>2674</v>
       </c>
@@ -13343,7 +13332,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>3317</v>
       </c>
@@ -13405,7 +13394,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>1445</v>
       </c>
@@ -13466,7 +13455,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="8" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>2503</v>
       </c>
@@ -13531,7 +13520,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>2503</v>
       </c>
@@ -13593,7 +13582,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="10" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>734</v>
       </c>
@@ -13660,7 +13649,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>734</v>
       </c>
@@ -13721,7 +13710,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="12" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>734</v>
       </c>
@@ -13783,7 +13772,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>734</v>
       </c>
@@ -13850,7 +13839,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>3414</v>
       </c>
@@ -13912,7 +13901,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="15" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>739</v>
       </c>
@@ -13979,7 +13968,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>739</v>
       </c>
@@ -14040,7 +14029,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="17" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>739</v>
       </c>
@@ -14107,7 +14096,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>739</v>
       </c>
@@ -14169,7 +14158,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="19" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>2528</v>
       </c>
@@ -14234,7 +14223,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>713</v>
       </c>
@@ -14303,7 +14292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>713</v>
       </c>
@@ -14370,7 +14359,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>2669</v>
       </c>
@@ -14435,7 +14424,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>2669</v>
       </c>
@@ -14497,7 +14486,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="24" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>719</v>
       </c>
@@ -14564,7 +14553,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>719</v>
       </c>
@@ -14631,7 +14620,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="26" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>719</v>
       </c>
@@ -14700,7 +14689,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>2777</v>
       </c>
@@ -14765,7 +14754,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>2777</v>
       </c>
@@ -14827,7 +14816,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="29" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>836</v>
       </c>
@@ -14894,7 +14883,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>836</v>
       </c>
@@ -14956,7 +14945,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>836</v>
       </c>
@@ -15023,7 +15012,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>1250</v>
       </c>
@@ -15090,7 +15079,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>1250</v>
       </c>
@@ -15152,7 +15141,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="34" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>841</v>
       </c>
@@ -15219,7 +15208,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>841</v>
       </c>
@@ -15286,7 +15275,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>841</v>
       </c>
@@ -15348,7 +15337,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="37" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>2623</v>
       </c>
@@ -15413,7 +15402,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>846</v>
       </c>
@@ -15480,7 +15469,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>846</v>
       </c>
@@ -15542,7 +15531,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>846</v>
       </c>
@@ -15609,7 +15598,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>3291</v>
       </c>
@@ -15671,7 +15660,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>1409</v>
       </c>
@@ -15740,7 +15729,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="43" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>1409</v>
       </c>
@@ -15807,7 +15796,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>3364</v>
       </c>
@@ -15869,7 +15858,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="45" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>1418</v>
       </c>
@@ -15936,7 +15925,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="46" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>1418</v>
       </c>
@@ -16003,7 +15992,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>2628</v>
       </c>
@@ -16068,7 +16057,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>2628</v>
       </c>
@@ -16127,7 +16116,7 @@
         <v>3484</v>
       </c>
     </row>
-    <row r="49" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>1372</v>
       </c>
@@ -16194,7 +16183,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="50" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>1372</v>
       </c>
@@ -16261,7 +16250,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="51" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>2408</v>
       </c>
@@ -16326,7 +16315,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="52" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>2408</v>
       </c>
@@ -16388,7 +16377,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="53" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>1377</v>
       </c>
@@ -16457,7 +16446,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="54" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>3381</v>
       </c>
@@ -16519,7 +16508,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="55" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>3381</v>
       </c>
@@ -16586,7 +16575,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="56" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>2548</v>
       </c>
@@ -16651,7 +16640,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>851</v>
       </c>
@@ -16718,7 +16707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>851</v>
       </c>
@@ -16785,7 +16774,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="59" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>851</v>
       </c>
@@ -16852,7 +16841,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="60" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>3360</v>
       </c>
@@ -16914,7 +16903,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="61" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>3360</v>
       </c>
@@ -16983,7 +16972,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="62" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>2538</v>
       </c>
@@ -17048,7 +17037,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="63" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
         <v>856</v>
       </c>
@@ -17115,7 +17104,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>856</v>
       </c>
@@ -17182,7 +17171,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="65" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
         <v>856</v>
       </c>
@@ -17249,7 +17238,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="66" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>2642</v>
       </c>
@@ -17314,7 +17303,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="67" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>2642</v>
       </c>
@@ -17376,7 +17365,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="68" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
         <v>3550</v>
       </c>
@@ -17445,7 +17434,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
         <v>861</v>
       </c>
@@ -17512,7 +17501,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>861</v>
       </c>
@@ -17574,7 +17563,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="71" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
         <v>861</v>
       </c>
@@ -17641,7 +17630,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="72" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>3455</v>
       </c>
@@ -17703,7 +17692,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="73" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
         <v>3734</v>
       </c>
@@ -17772,7 +17761,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="74" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
         <v>864</v>
       </c>
@@ -17839,7 +17828,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>864</v>
       </c>
@@ -17901,7 +17890,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="76" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
         <v>864</v>
       </c>
@@ -17968,7 +17957,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="77" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>864</v>
       </c>
@@ -18030,7 +18019,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="78" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
         <v>3992</v>
       </c>
@@ -18099,7 +18088,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="79" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>869</v>
       </c>
@@ -18166,7 +18155,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
         <v>869</v>
       </c>
@@ -18233,7 +18222,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="81" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
         <v>869</v>
       </c>
@@ -18300,7 +18289,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="82" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>2755</v>
       </c>
@@ -18365,7 +18354,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="83" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>2755</v>
       </c>
@@ -18427,7 +18416,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="84" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
         <v>2755</v>
       </c>
@@ -18496,7 +18485,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="85" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
         <v>874</v>
       </c>
@@ -18563,7 +18552,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
         <v>874</v>
       </c>
@@ -18632,7 +18621,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="87" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>874</v>
       </c>
@@ -18691,7 +18680,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="88" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>2651</v>
       </c>
@@ -18756,7 +18745,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="89" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
         <v>2651</v>
       </c>
@@ -18825,7 +18814,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="90" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>2880</v>
       </c>
@@ -18887,7 +18876,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="91" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
         <v>2880</v>
       </c>
@@ -18954,7 +18943,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="92" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
         <v>1256</v>
       </c>
@@ -19021,7 +19010,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="93" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>1256</v>
       </c>
@@ -19083,7 +19072,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="94" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
         <v>1256</v>
       </c>
@@ -19152,7 +19141,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="95" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
         <v>3225</v>
       </c>
@@ -19219,7 +19208,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="96" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
         <v>1306</v>
       </c>
@@ -19286,7 +19275,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="97" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>1306</v>
       </c>
@@ -19348,7 +19337,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="98" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
         <v>1306</v>
       </c>
@@ -19417,7 +19406,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="99" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>2543</v>
       </c>
@@ -19482,7 +19471,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="100" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
         <v>879</v>
       </c>
@@ -19549,7 +19538,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
         <v>879</v>
       </c>
@@ -19616,7 +19605,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="102" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B102" s="1" t="s">
         <v>1278</v>
       </c>
@@ -19683,7 +19672,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="103" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>1278</v>
       </c>
@@ -19745,7 +19734,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="104" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>1278</v>
       </c>
@@ -19807,7 +19796,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="105" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
         <v>1278</v>
       </c>
@@ -19876,7 +19865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
         <v>884</v>
       </c>
@@ -19943,7 +19932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
         <v>884</v>
       </c>
@@ -20012,7 +20001,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="108" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
         <v>884</v>
       </c>
@@ -20079,7 +20068,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="109" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>884</v>
       </c>
@@ -20138,7 +20127,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="110" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>2656</v>
       </c>
@@ -20203,7 +20192,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="111" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
         <v>2656</v>
       </c>
@@ -20272,7 +20261,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="112" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
         <v>889</v>
       </c>
@@ -20341,7 +20330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B113" s="1" t="s">
         <v>889</v>
       </c>
@@ -20408,7 +20397,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="114" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>889</v>
       </c>
@@ -20470,7 +20459,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="115" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B115" s="1" t="s">
         <v>889</v>
       </c>
@@ -20537,7 +20526,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="116" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>3377</v>
       </c>
@@ -20599,7 +20588,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="117" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B117" s="1" t="s">
         <v>3377</v>
       </c>
@@ -20668,7 +20657,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="118" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B118" s="1" t="s">
         <v>895</v>
       </c>
@@ -20735,7 +20724,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>895</v>
       </c>
@@ -20800,7 +20789,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="120" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B120" s="1" t="s">
         <v>895</v>
       </c>
@@ -20867,7 +20856,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="121" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>3388</v>
       </c>
@@ -20929,7 +20918,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="122" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B122" s="1" t="s">
         <v>3388</v>
       </c>
@@ -20998,7 +20987,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="123" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B123" s="1" t="s">
         <v>1218</v>
       </c>
@@ -21065,7 +21054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B124" s="1" t="s">
         <v>1218</v>
       </c>
@@ -21126,7 +21115,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="125" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B125" s="1" t="s">
         <v>1218</v>
       </c>
@@ -21193,7 +21182,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="126" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>2760</v>
       </c>
@@ -21258,7 +21247,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="127" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>2760</v>
       </c>
@@ -21320,7 +21309,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="128" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B128" s="1" t="s">
         <v>3743</v>
       </c>
@@ -21389,7 +21378,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="129" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B129" s="1" t="s">
         <v>916</v>
       </c>
@@ -21456,7 +21445,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B130" s="1" t="s">
         <v>916</v>
       </c>
@@ -21523,7 +21512,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="131" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
         <v>1270</v>
       </c>
@@ -21590,7 +21579,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="132" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>1270</v>
       </c>
@@ -21655,7 +21644,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="133" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>1270</v>
       </c>
@@ -21717,7 +21706,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="134" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
         <v>3569</v>
       </c>
@@ -21786,7 +21775,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
         <v>921</v>
       </c>
@@ -21853,7 +21842,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
         <v>921</v>
       </c>
@@ -21975,7 +21964,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="138" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
         <v>1266</v>
       </c>
@@ -22042,7 +22031,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="139" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
         <v>1266</v>
       </c>
@@ -22107,7 +22096,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="140" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
         <v>926</v>
       </c>
@@ -22174,7 +22163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
         <v>926</v>
       </c>
@@ -22243,7 +22232,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="142" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
         <v>926</v>
       </c>
@@ -22310,7 +22299,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="143" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
         <v>2580</v>
       </c>
@@ -22375,7 +22364,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="144" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>2580</v>
       </c>
@@ -22437,7 +22426,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="145" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
         <v>2580</v>
       </c>
@@ -22506,7 +22495,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="146" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
         <v>1191</v>
       </c>
@@ -22573,7 +22562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
         <v>1191</v>
       </c>
@@ -22642,7 +22631,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="148" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
         <v>1191</v>
       </c>
@@ -22711,7 +22700,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="149" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
         <v>2459</v>
       </c>
@@ -22776,7 +22765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
         <v>2459</v>
       </c>
@@ -22838,7 +22827,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="151" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B151" s="1" t="s">
         <v>2459</v>
       </c>
@@ -22907,7 +22896,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="152" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B152" s="1" t="s">
         <v>728</v>
       </c>
@@ -22974,7 +22963,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="153" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B153" s="1" t="s">
         <v>728</v>
       </c>
@@ -23043,7 +23032,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="154" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
         <v>3899</v>
       </c>
@@ -23112,7 +23101,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="155" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B155" s="1" t="s">
         <v>578</v>
       </c>
@@ -23175,7 +23164,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="156" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B156" s="1" t="s">
         <v>578</v>
       </c>
@@ -23244,7 +23233,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="157" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
         <v>2386</v>
       </c>
@@ -23309,7 +23298,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="158" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B158" s="1" t="s">
         <v>2386</v>
       </c>
@@ -23378,7 +23367,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="159" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
         <v>3339</v>
       </c>
@@ -23440,7 +23429,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="160" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
         <v>584</v>
       </c>
@@ -23507,7 +23496,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="161" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
         <v>584</v>
       </c>
@@ -23575,7 +23564,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="162" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B162" s="1" t="s">
         <v>584</v>
       </c>
@@ -23642,7 +23631,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="163" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
         <v>584</v>
       </c>
@@ -23704,7 +23693,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="164" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B164" s="1" t="s">
         <v>1274</v>
       </c>
@@ -23771,7 +23760,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="165" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
         <v>1274</v>
       </c>
@@ -23840,7 +23829,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="166" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
         <v>590</v>
       </c>
@@ -23903,7 +23892,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="167" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
         <v>590</v>
       </c>
@@ -23965,7 +23954,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="168" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
         <v>590</v>
       </c>
@@ -24032,7 +24021,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="169" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
         <v>590</v>
       </c>
@@ -24091,7 +24080,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="170" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
         <v>1293</v>
       </c>
@@ -24158,7 +24147,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="171" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
         <v>1293</v>
       </c>
@@ -24227,7 +24216,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="172" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
         <v>596</v>
       </c>
@@ -24290,7 +24279,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="173" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B173" s="1" t="s">
         <v>596</v>
       </c>
@@ -24357,7 +24346,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="174" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
         <v>596</v>
       </c>
@@ -24424,7 +24413,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="175" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
         <v>2079</v>
       </c>
@@ -24493,7 +24482,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="176" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
         <v>2079</v>
       </c>
@@ -24558,7 +24547,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="177" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
         <v>2079</v>
       </c>
@@ -24620,7 +24609,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="178" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
         <v>3693</v>
       </c>
@@ -24689,7 +24678,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="179" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B179" s="1" t="s">
         <v>911</v>
       </c>
@@ -24756,7 +24745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="180" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
         <v>911</v>
       </c>
@@ -24823,7 +24812,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="181" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B181" s="1" t="s">
         <v>911</v>
       </c>
@@ -24890,7 +24879,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="182" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
         <v>2533</v>
       </c>
@@ -24955,7 +24944,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="183" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
         <v>3295</v>
       </c>
@@ -25017,7 +25006,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="184" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B184" s="1" t="s">
         <v>3295</v>
       </c>
@@ -25086,7 +25075,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="185" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B185" s="1" t="s">
         <v>602</v>
       </c>
@@ -25149,7 +25138,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="186" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B186" s="1" t="s">
         <v>602</v>
       </c>
@@ -25210,7 +25199,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="187" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B187" s="1" t="s">
         <v>602</v>
       </c>
@@ -25277,7 +25266,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="188" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
         <v>2391</v>
       </c>
@@ -25342,7 +25331,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="189" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>2391</v>
       </c>
@@ -25404,7 +25393,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="190" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B190" s="1" t="s">
         <v>3592</v>
       </c>
@@ -25473,7 +25462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="191" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B191" s="1" t="s">
         <v>608</v>
       </c>
@@ -25536,7 +25525,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="192" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B192" s="1" t="s">
         <v>608</v>
       </c>
@@ -25597,7 +25586,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="193" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B193" s="1" t="s">
         <v>608</v>
       </c>
@@ -25664,7 +25653,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="194" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
         <v>2454</v>
       </c>
@@ -25729,7 +25718,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="195" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
         <v>2454</v>
       </c>
@@ -25791,7 +25780,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="196" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B196" s="1" t="s">
         <v>2454</v>
       </c>
@@ -25860,7 +25849,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="197" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B197" s="1" t="s">
         <v>614</v>
       </c>
@@ -25923,7 +25912,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="198" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B198" s="1" t="s">
         <v>614</v>
       </c>
@@ -25992,7 +25981,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="199" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B199" s="1" t="s">
         <v>614</v>
       </c>
@@ -26059,7 +26048,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="200" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
         <v>2517</v>
       </c>
@@ -26124,7 +26113,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="201" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B201" s="1" t="s">
         <v>2517</v>
       </c>
@@ -26193,7 +26182,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="202" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
         <v>3349</v>
       </c>
@@ -26255,7 +26244,7 @@
         <v>3353</v>
       </c>
     </row>
-    <row r="203" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B203" s="1" t="s">
         <v>905</v>
       </c>
@@ -26318,7 +26307,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="204" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B204" s="1" t="s">
         <v>905</v>
       </c>
@@ -26387,7 +26376,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="205" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B205" s="1" t="s">
         <v>905</v>
       </c>
@@ -26454,7 +26443,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="206" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
         <v>905</v>
       </c>
@@ -26516,7 +26505,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="207" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>2440</v>
       </c>
@@ -26581,7 +26570,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="208" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B208" s="1" t="s">
         <v>2440</v>
       </c>
@@ -26650,7 +26639,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="209" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B209" s="1" t="s">
         <v>620</v>
       </c>
@@ -26713,7 +26702,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="210" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B210" s="1" t="s">
         <v>620</v>
       </c>
@@ -26780,7 +26769,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="211" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B211" s="1" t="s">
         <v>620</v>
       </c>
@@ -26847,7 +26836,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="212" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B212" s="1" t="s">
         <v>3904</v>
       </c>
@@ -26916,7 +26905,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="213" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B213" s="1" t="s">
         <v>626</v>
       </c>
@@ -26983,7 +26972,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="214" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B214" s="1" t="s">
         <v>626</v>
       </c>
@@ -27052,7 +27041,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="215" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B215" s="1" t="s">
         <v>626</v>
       </c>
@@ -27119,7 +27108,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="216" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
         <v>626</v>
       </c>
@@ -27178,7 +27167,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="217" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B217" s="1" t="s">
         <v>3878</v>
       </c>
@@ -27247,7 +27236,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="218" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B218" s="1" t="s">
         <v>632</v>
       </c>
@@ -27310,7 +27299,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="219" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B219" s="1" t="s">
         <v>632</v>
       </c>
@@ -27379,7 +27368,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="220" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B220" s="1" t="s">
         <v>632</v>
       </c>
@@ -27446,7 +27435,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="221" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B221" s="1" t="s">
         <v>632</v>
       </c>
@@ -27513,7 +27502,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="222" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
         <v>3284</v>
       </c>
@@ -27575,7 +27564,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="223" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B223" s="1" t="s">
         <v>638</v>
       </c>
@@ -27638,7 +27627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="224" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B224" s="1" t="s">
         <v>638</v>
       </c>
@@ -27707,7 +27696,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="225" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
         <v>638</v>
       </c>
@@ -27772,7 +27761,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="226" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B226" s="1" t="s">
         <v>638</v>
       </c>
@@ -27839,7 +27828,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="227" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
         <v>638</v>
       </c>
@@ -27898,7 +27887,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="228" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B228" s="1" t="s">
         <v>3983</v>
       </c>
@@ -27967,7 +27956,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="229" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B229" s="1" t="s">
         <v>900</v>
       </c>
@@ -28034,7 +28023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="230" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B230" s="1" t="s">
         <v>900</v>
       </c>
@@ -28103,7 +28092,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="231" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
         <v>900</v>
       </c>
@@ -28165,7 +28154,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="232" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B232" s="1" t="s">
         <v>900</v>
       </c>
@@ -28232,7 +28221,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="233" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
         <v>900</v>
       </c>
@@ -28291,7 +28280,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="234" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B234" s="1" t="s">
         <v>3945</v>
       </c>
@@ -28360,7 +28349,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="235" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B235" s="1" t="s">
         <v>1804</v>
       </c>
@@ -28429,7 +28418,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="236" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B236" s="1" t="s">
         <v>548</v>
       </c>
@@ -28492,7 +28481,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="237" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B237" s="1" t="s">
         <v>548</v>
       </c>
@@ -28561,7 +28550,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="238" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B238" s="1" t="s">
         <v>1852</v>
       </c>
@@ -28630,7 +28619,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="239" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>1852</v>
       </c>
@@ -28695,7 +28684,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="240" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
         <v>1852</v>
       </c>
@@ -28757,7 +28746,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="241" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B241" s="1" t="s">
         <v>3687</v>
       </c>
@@ -28826,7 +28815,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="242" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B242" s="1" t="s">
         <v>554</v>
       </c>
@@ -28889,7 +28878,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="243" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B243" s="1" t="s">
         <v>554</v>
       </c>
@@ -28958,7 +28947,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="244" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B244" s="1" t="s">
         <v>554</v>
       </c>
@@ -29025,7 +29014,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="245" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B245" s="1" t="s">
         <v>2084</v>
       </c>
@@ -29094,7 +29083,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="246" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
         <v>2084</v>
       </c>
@@ -29159,7 +29148,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="247" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
         <v>2084</v>
       </c>
@@ -29221,7 +29210,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="248" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B248" s="1" t="s">
         <v>2084</v>
       </c>
@@ -29290,7 +29279,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="249" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B249" s="1" t="s">
         <v>560</v>
       </c>
@@ -29353,7 +29342,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="250" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B250" s="1" t="s">
         <v>560</v>
       </c>
@@ -29420,7 +29409,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="251" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
         <v>560</v>
       </c>
@@ -29485,7 +29474,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="252" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B252" s="1" t="s">
         <v>560</v>
       </c>
@@ -29552,7 +29541,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="253" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B253" s="1" t="s">
         <v>1553</v>
       </c>
@@ -29621,7 +29610,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="254" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B254" s="1" t="s">
         <v>3712</v>
       </c>
@@ -29690,7 +29679,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="255" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B255" s="1" t="s">
         <v>566</v>
       </c>
@@ -29753,7 +29742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B256" s="1" t="s">
         <v>566</v>
       </c>
@@ -29822,7 +29811,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="257" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B257" s="1" t="s">
         <v>566</v>
       </c>
@@ -29889,7 +29878,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="258" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
         <v>566</v>
       </c>
@@ -29951,7 +29940,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="259" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B259" s="1" t="s">
         <v>2053</v>
       </c>
@@ -30020,7 +30009,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="260" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
         <v>2053</v>
       </c>
@@ -30085,7 +30074,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="261" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B261" s="1" t="s">
         <v>2053</v>
       </c>
@@ -30154,7 +30143,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="262" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B262" s="1" t="s">
         <v>785</v>
       </c>
@@ -30221,7 +30210,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="263" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B263" s="1" t="s">
         <v>785</v>
       </c>
@@ -30290,7 +30279,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="264" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B264" s="1" t="s">
         <v>785</v>
       </c>
@@ -30357,7 +30346,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="265" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B265" s="1" t="s">
         <v>1858</v>
       </c>
@@ -30426,7 +30415,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="266" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
         <v>1858</v>
       </c>
@@ -30491,7 +30480,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="267" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
         <v>1858</v>
       </c>
@@ -30553,7 +30542,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="268" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B268" s="1" t="s">
         <v>1858</v>
       </c>
@@ -30622,7 +30611,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="269" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B269" s="1" t="s">
         <v>1364</v>
       </c>
@@ -30687,7 +30676,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="270" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B270" s="1" t="s">
         <v>1364</v>
       </c>
@@ -30754,7 +30743,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="271" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B271" s="1" t="s">
         <v>1364</v>
       </c>
@@ -30821,7 +30810,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="272" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
         <v>1364</v>
       </c>
@@ -30883,7 +30872,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="273" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
         <v>2745</v>
       </c>
@@ -30948,7 +30937,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="274" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B274" s="1" t="s">
         <v>2745</v>
       </c>
@@ -31017,7 +31006,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="275" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B275" s="1" t="s">
         <v>1325</v>
       </c>
@@ -31086,7 +31075,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="276" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B276" s="1" t="s">
         <v>1325</v>
       </c>
@@ -31153,7 +31142,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="277" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
         <v>1325</v>
       </c>
@@ -31215,7 +31204,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="278" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B278" s="1" t="s">
         <v>1967</v>
       </c>
@@ -31284,7 +31273,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="279" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
         <v>1967</v>
       </c>
@@ -31346,7 +31335,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="280" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B280" s="1" t="s">
         <v>1967</v>
       </c>
@@ -31415,7 +31404,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="281" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B281" s="1" t="s">
         <v>572</v>
       </c>
@@ -31478,7 +31467,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B282" s="1" t="s">
         <v>572</v>
       </c>
@@ -31547,7 +31536,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="283" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B283" s="1" t="s">
         <v>572</v>
       </c>
@@ -31616,7 +31605,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="284" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B284" s="1" t="s">
         <v>572</v>
       </c>
@@ -31683,7 +31672,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="285" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
         <v>2803</v>
       </c>
@@ -31748,7 +31737,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="286" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
         <v>2803</v>
       </c>
@@ -31810,7 +31799,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="287" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B287" s="1" t="s">
         <v>770</v>
       </c>
@@ -31877,7 +31866,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="288" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B288" s="1" t="s">
         <v>770</v>
       </c>
@@ -31944,7 +31933,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="289" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B289" s="1" t="s">
         <v>770</v>
       </c>
@@ -32011,7 +32000,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="290" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B290" s="1" t="s">
         <v>770</v>
       </c>
@@ -32078,7 +32067,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="291" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
         <v>2523</v>
       </c>
@@ -32143,7 +32132,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="292" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B292" s="1" t="s">
         <v>3648</v>
       </c>
@@ -32212,7 +32201,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="293" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B293" s="1" t="s">
         <v>775</v>
       </c>
@@ -32279,7 +32268,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="294" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B294" s="1" t="s">
         <v>775</v>
       </c>
@@ -32346,7 +32335,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="295" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B295" s="1" t="s">
         <v>1471</v>
       </c>
@@ -32415,7 +32404,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="296" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
         <v>1471</v>
       </c>
@@ -32480,7 +32469,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="297" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B297" s="1" t="s">
         <v>1471</v>
       </c>
@@ -32549,7 +32538,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="298" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B298" s="1" t="s">
         <v>1282</v>
       </c>
@@ -32616,7 +32605,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="299" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
         <v>1282</v>
       </c>
@@ -32678,7 +32667,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="300" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B300" s="1" t="s">
         <v>1282</v>
       </c>
@@ -32745,7 +32734,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="301" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B301" t="s">
         <v>3427</v>
       </c>
@@ -32807,7 +32796,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="302" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B302" s="1" t="s">
         <v>3427</v>
       </c>
@@ -32876,7 +32865,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="303" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B303" s="1" t="s">
         <v>1261</v>
       </c>
@@ -32943,7 +32932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="304" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B304" s="1" t="s">
         <v>1261</v>
       </c>
@@ -33010,7 +32999,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="305" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B305" t="s">
         <v>1261</v>
       </c>
@@ -33072,7 +33061,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="306" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B306" s="1" t="s">
         <v>1950</v>
       </c>
@@ -33141,7 +33130,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="307" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B307" t="s">
         <v>1950</v>
       </c>
@@ -33206,7 +33195,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="308" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B308" s="1" t="s">
         <v>3761</v>
       </c>
@@ -33275,7 +33264,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="309" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B309" s="1" t="s">
         <v>780</v>
       </c>
@@ -33342,7 +33331,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="310" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B310" t="s">
         <v>780</v>
       </c>
@@ -33407,7 +33396,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="311" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B311" s="1" t="s">
         <v>780</v>
       </c>
@@ -33474,7 +33463,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="312" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B312" t="s">
         <v>3401</v>
       </c>
@@ -33536,7 +33525,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="313" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B313" s="1" t="s">
         <v>3401</v>
       </c>
@@ -33605,7 +33594,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="314" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B314" s="1" t="s">
         <v>1196</v>
       </c>
@@ -33672,7 +33661,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="315" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B315" s="1" t="s">
         <v>1196</v>
       </c>
@@ -33743,7 +33732,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="316" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B316" t="s">
         <v>1196</v>
       </c>
@@ -33805,7 +33794,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="317" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B317" s="1" t="s">
         <v>1196</v>
       </c>
@@ -33872,7 +33861,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="318" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B318" s="1" t="s">
         <v>790</v>
       </c>
@@ -33939,7 +33928,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="319" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B319" t="s">
         <v>790</v>
       </c>
@@ -34001,7 +33990,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="320" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B320" s="1" t="s">
         <v>790</v>
       </c>
@@ -34068,7 +34057,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="321" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B321" s="1" t="s">
         <v>1502</v>
       </c>
@@ -34137,7 +34126,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="322" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B322" t="s">
         <v>1502</v>
       </c>
@@ -34199,7 +34188,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="323" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B323" s="1" t="s">
         <v>1502</v>
       </c>
@@ -34268,7 +34257,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="324" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B324" s="1" t="s">
         <v>795</v>
       </c>
@@ -34335,7 +34324,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="325" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>795</v>
       </c>
@@ -34397,7 +34386,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="326" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B326" s="1" t="s">
         <v>795</v>
       </c>
@@ -34464,7 +34453,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="327" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B327" s="1" t="s">
         <v>1863</v>
       </c>
@@ -34533,7 +34522,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="328" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B328" t="s">
         <v>1863</v>
       </c>
@@ -34595,7 +34584,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="329" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B329" s="1" t="s">
         <v>1863</v>
       </c>
@@ -34664,7 +34653,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="330" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B330" s="1" t="s">
         <v>800</v>
       </c>
@@ -34731,7 +34720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="331" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B331" t="s">
         <v>800</v>
       </c>
@@ -34793,7 +34782,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="332" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B332" s="1" t="s">
         <v>800</v>
       </c>
@@ -34860,7 +34849,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="333" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B333" s="1" t="s">
         <v>1662</v>
       </c>
@@ -34929,7 +34918,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="334" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B334" t="s">
         <v>1662</v>
       </c>
@@ -34988,7 +34977,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="335" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B335" s="1" t="s">
         <v>1662</v>
       </c>
@@ -35057,7 +35046,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="336" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B336" s="1" t="s">
         <v>805</v>
       </c>
@@ -35124,7 +35113,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="337" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B337" s="1" t="s">
         <v>805</v>
       </c>
@@ -35191,7 +35180,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="338" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B338" s="1" t="s">
         <v>2146</v>
       </c>
@@ -35260,7 +35249,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="339" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B339" t="s">
         <v>2146</v>
       </c>
@@ -35325,7 +35314,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="340" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B340" t="s">
         <v>2146</v>
       </c>
@@ -35387,7 +35376,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="341" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B341" s="1" t="s">
         <v>2146</v>
       </c>
@@ -35456,7 +35445,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="342" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B342" s="1" t="s">
         <v>1207</v>
       </c>
@@ -35525,7 +35514,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="343" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B343" s="1" t="s">
         <v>1207</v>
       </c>
@@ -35592,7 +35581,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="344" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B344" s="1" t="s">
         <v>1930</v>
       </c>
@@ -35661,7 +35650,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="345" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B345" t="s">
         <v>1930</v>
       </c>
@@ -35726,7 +35715,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="346" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B346" t="s">
         <v>1930</v>
       </c>
@@ -35788,7 +35777,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="347" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B347" s="1" t="s">
         <v>1930</v>
       </c>
@@ -35857,7 +35846,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="348" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B348" s="1" t="s">
         <v>810</v>
       </c>
@@ -35924,7 +35913,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="349" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B349" t="s">
         <v>810</v>
       </c>
@@ -35989,7 +35978,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="350" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B350" s="1" t="s">
         <v>810</v>
       </c>
@@ -36056,7 +36045,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="351" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B351" s="1" t="s">
         <v>1956</v>
       </c>
@@ -36125,7 +36114,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="352" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B352" s="1" t="s">
         <v>3111</v>
       </c>
@@ -36192,7 +36181,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="353" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B353" s="1" t="s">
         <v>1962</v>
       </c>
@@ -36261,7 +36250,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="354" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>1962</v>
       </c>
@@ -36326,7 +36315,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="355" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B355" t="s">
         <v>1962</v>
       </c>
@@ -36382,7 +36371,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="356" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B356" s="1" t="s">
         <v>2334</v>
       </c>
@@ -36449,7 +36438,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="357" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B357" s="1" t="s">
         <v>2334</v>
       </c>
@@ -36516,7 +36505,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="358" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B358" t="s">
         <v>2553</v>
       </c>
@@ -36581,7 +36570,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="359" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B359" t="s">
         <v>2553</v>
       </c>
@@ -36643,7 +36632,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="360" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B360" s="1" t="s">
         <v>2553</v>
       </c>
@@ -36712,7 +36701,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="361" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B361" s="1" t="s">
         <v>815</v>
       </c>
@@ -36779,7 +36768,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="362" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B362" t="s">
         <v>2585</v>
       </c>
@@ -36844,7 +36833,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="363" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B363" s="1" t="s">
         <v>2585</v>
       </c>
@@ -36913,7 +36902,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="364" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B364" s="1" t="s">
         <v>820</v>
       </c>
@@ -36980,7 +36969,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="365" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B365" s="1" t="s">
         <v>820</v>
       </c>
@@ -37047,7 +37036,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="366" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B366" t="s">
         <v>820</v>
       </c>
@@ -37109,7 +37098,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="367" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B367" s="1" t="s">
         <v>1761</v>
       </c>
@@ -37178,7 +37167,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="368" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B368" t="s">
         <v>1761</v>
       </c>
@@ -37243,7 +37232,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="369" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B369" s="1" t="s">
         <v>1761</v>
       </c>
@@ -37312,7 +37301,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="370" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B370" s="1" t="s">
         <v>825</v>
       </c>
@@ -37379,7 +37368,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="371" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B371" s="1" t="s">
         <v>825</v>
       </c>
@@ -37446,7 +37435,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="372" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B372" s="1" t="s">
         <v>825</v>
       </c>
@@ -37513,7 +37502,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="373" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B373" s="1" t="s">
         <v>825</v>
       </c>
@@ -37582,7 +37571,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="374" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B374" t="s">
         <v>2468</v>
       </c>
@@ -37647,7 +37636,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="375" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B375" t="s">
         <v>2468</v>
       </c>
@@ -37709,7 +37698,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="376" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B376" s="1" t="s">
         <v>830</v>
       </c>
@@ -37772,7 +37761,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="377" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B377" s="1" t="s">
         <v>830</v>
       </c>
@@ -37839,7 +37828,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="378" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B378" s="1" t="s">
         <v>830</v>
       </c>
@@ -37906,7 +37895,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="379" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B379" s="1" t="s">
         <v>2014</v>
       </c>
@@ -37975,7 +37964,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="380" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B380" t="s">
         <v>2014</v>
       </c>
@@ -38037,7 +38026,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="381" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B381" t="s">
         <v>2014</v>
       </c>
@@ -38099,7 +38088,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="382" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B382" s="1" t="s">
         <v>536</v>
       </c>
@@ -38162,7 +38151,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="383" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B383" t="s">
         <v>536</v>
       </c>
@@ -38224,7 +38213,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="384" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B384" s="1" t="s">
         <v>536</v>
       </c>
@@ -38291,7 +38280,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="385" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B385" s="1" t="s">
         <v>1918</v>
       </c>
@@ -38360,7 +38349,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="386" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B386" t="s">
         <v>1918</v>
       </c>
@@ -38425,7 +38414,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="387" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B387" s="1" t="s">
         <v>542</v>
       </c>
@@ -38488,7 +38477,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="388" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B388" s="1" t="s">
         <v>542</v>
       </c>
@@ -38555,7 +38544,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="389" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B389" s="1" t="s">
         <v>542</v>
       </c>
@@ -38622,7 +38611,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="390" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B390" t="s">
         <v>542</v>
       </c>
@@ -38687,7 +38676,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="391" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B391" s="1" t="s">
         <v>542</v>
       </c>
@@ -38754,7 +38743,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="392" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B392" t="s">
         <v>2750</v>
       </c>
@@ -38819,7 +38808,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="393" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B393" s="1" t="s">
         <v>428</v>
       </c>
@@ -38882,7 +38871,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="394" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B394" s="1" t="s">
         <v>428</v>
       </c>
@@ -38949,7 +38938,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="395" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B395" s="1" t="s">
         <v>428</v>
       </c>
@@ -39016,7 +39005,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="396" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B396" s="1" t="s">
         <v>1875</v>
       </c>
@@ -39085,7 +39074,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="397" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B397" t="s">
         <v>1875</v>
       </c>
@@ -39150,7 +39139,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="398" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B398" s="1" t="s">
         <v>434</v>
       </c>
@@ -39213,7 +39202,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="399" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B399" s="1" t="s">
         <v>434</v>
       </c>
@@ -39280,7 +39269,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="400" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B400" t="s">
         <v>434</v>
       </c>
@@ -39342,7 +39331,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="401" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B401" s="1" t="s">
         <v>434</v>
       </c>
@@ -39409,7 +39398,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="402" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B402" t="s">
         <v>2724</v>
       </c>
@@ -39474,7 +39463,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="403" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B403" s="1" t="s">
         <v>722</v>
       </c>
@@ -39537,7 +39526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="404" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B404" s="1" t="s">
         <v>722</v>
       </c>
@@ -39604,7 +39593,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="405" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B405" s="1" t="s">
         <v>1656</v>
       </c>
@@ -39673,7 +39662,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="406" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B406" s="1" t="s">
         <v>3030</v>
       </c>
@@ -39740,7 +39729,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="407" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B407" s="1" t="s">
         <v>530</v>
       </c>
@@ -39803,7 +39792,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="408" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B408" s="1" t="s">
         <v>530</v>
       </c>
@@ -39870,7 +39859,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="409" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B409" s="1" t="s">
         <v>530</v>
       </c>
@@ -39937,7 +39926,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="410" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B410" s="1" t="s">
         <v>2910</v>
       </c>
@@ -40004,7 +39993,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="411" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B411" t="s">
         <v>2512</v>
       </c>
@@ -40069,7 +40058,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="412" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B412" s="1" t="s">
         <v>440</v>
       </c>
@@ -40132,7 +40121,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="413" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B413" s="1" t="s">
         <v>440</v>
       </c>
@@ -40199,7 +40188,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="414" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B414" s="1" t="s">
         <v>440</v>
       </c>
@@ -40266,7 +40255,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="415" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B415" s="1" t="s">
         <v>1712</v>
       </c>
@@ -40335,7 +40324,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="416" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B416" t="s">
         <v>1712</v>
       </c>
@@ -40400,7 +40389,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="417" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B417" s="1" t="s">
         <v>749</v>
       </c>
@@ -40467,7 +40456,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="418" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B418" s="1" t="s">
         <v>749</v>
       </c>
@@ -40534,7 +40523,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="419" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B419" s="1" t="s">
         <v>2036</v>
       </c>
@@ -40603,7 +40592,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="420" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B420" t="s">
         <v>2036</v>
       </c>
@@ -40668,7 +40657,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="421" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B421" s="1" t="s">
         <v>2968</v>
       </c>
@@ -40735,7 +40724,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="422" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B422" s="1" t="s">
         <v>754</v>
       </c>
@@ -40802,7 +40791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="423" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B423" s="1" t="s">
         <v>754</v>
       </c>
@@ -40869,7 +40858,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="424" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B424" s="1" t="s">
         <v>1846</v>
       </c>
@@ -40938,7 +40927,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="425" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B425" t="s">
         <v>1846</v>
       </c>
@@ -41003,7 +40992,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="426" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B426" s="1" t="s">
         <v>3034</v>
       </c>
@@ -41070,7 +41059,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="427" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B427" s="1" t="s">
         <v>524</v>
       </c>
@@ -41133,7 +41122,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="428" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B428" s="1" t="s">
         <v>2105</v>
       </c>
@@ -41202,7 +41191,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="429" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B429" s="1" t="s">
         <v>2105</v>
       </c>
@@ -41271,7 +41260,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="430" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B430" s="1" t="s">
         <v>2991</v>
       </c>
@@ -41338,7 +41327,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="431" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B431" s="1" t="s">
         <v>744</v>
       </c>
@@ -41405,7 +41394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="432" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B432" s="1" t="s">
         <v>1935</v>
       </c>
@@ -41474,7 +41463,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="433" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B433" t="s">
         <v>1935</v>
       </c>
@@ -41539,7 +41528,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="434" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B434" s="1" t="s">
         <v>1935</v>
       </c>
@@ -41606,7 +41595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="435" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B435" s="1" t="s">
         <v>1935</v>
       </c>
@@ -41675,7 +41664,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="436" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B436" s="1" t="s">
         <v>1201</v>
       </c>
@@ -41744,7 +41733,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="437" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B437" s="1" t="s">
         <v>2168</v>
       </c>
@@ -41813,7 +41802,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="438" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B438" s="1" t="s">
         <v>3010</v>
       </c>
@@ -41880,7 +41869,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="439" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B439" s="1" t="s">
         <v>1113</v>
       </c>
@@ -41947,7 +41936,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="440" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B440" s="1" t="s">
         <v>1717</v>
       </c>
@@ -42016,7 +42005,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="441" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B441" s="1" t="s">
         <v>1717</v>
       </c>
@@ -42085,7 +42074,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="442" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B442" t="s">
         <v>2370</v>
       </c>
@@ -42150,7 +42139,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="443" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B443" s="1" t="s">
         <v>2370</v>
       </c>
@@ -42217,7 +42206,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="444" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B444" s="1" t="s">
         <v>679</v>
       </c>
@@ -42280,7 +42269,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="445" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B445" s="1" t="s">
         <v>1913</v>
       </c>
@@ -42349,7 +42338,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="446" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B446" t="s">
         <v>1913</v>
       </c>
@@ -42414,7 +42403,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="447" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B447" s="1" t="s">
         <v>1913</v>
       </c>
@@ -42483,7 +42472,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="448" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B448" s="1" t="s">
         <v>3026</v>
       </c>
@@ -42550,7 +42539,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="449" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B449" s="1" t="s">
         <v>446</v>
       </c>
@@ -42613,7 +42602,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="450" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B450" s="1" t="s">
         <v>446</v>
       </c>
@@ -42678,7 +42667,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="451" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B451" s="1" t="s">
         <v>1751</v>
       </c>
@@ -42747,7 +42736,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="452" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B452" t="s">
         <v>1751</v>
       </c>
@@ -42812,7 +42801,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="453" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B453" s="1" t="s">
         <v>1751</v>
       </c>
@@ -42879,7 +42868,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="454" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B454" t="s">
         <v>1751</v>
       </c>
@@ -42941,7 +42930,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="455" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B455" s="1" t="s">
         <v>452</v>
       </c>
@@ -43004,7 +42993,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="456" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B456" s="1" t="s">
         <v>452</v>
       </c>
@@ -43069,7 +43058,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="457" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B457" t="s">
         <v>2571</v>
       </c>
@@ -43134,7 +43123,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="458" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B458" s="1" t="s">
         <v>1487</v>
       </c>
@@ -43203,7 +43192,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="459" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B459" s="1" t="s">
         <v>1487</v>
       </c>
@@ -43270,7 +43259,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="460" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B460" s="1" t="s">
         <v>512</v>
       </c>
@@ -43333,7 +43322,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="461" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B461" t="s">
         <v>512</v>
       </c>
@@ -43398,7 +43387,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="462" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B462" s="1" t="s">
         <v>512</v>
       </c>
@@ -43463,7 +43452,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="463" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B463" s="1" t="s">
         <v>2229</v>
       </c>
@@ -43530,7 +43519,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="464" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B464" t="s">
         <v>2229</v>
       </c>
@@ -43592,7 +43581,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="465" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B465" s="1" t="s">
         <v>2987</v>
       </c>
@@ -43659,7 +43648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="466" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B466" s="1" t="s">
         <v>518</v>
       </c>
@@ -43722,7 +43711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="467" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B467" s="1" t="s">
         <v>518</v>
       </c>
@@ -43787,7 +43776,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="468" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B468" t="s">
         <v>2633</v>
       </c>
@@ -43852,7 +43841,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="469" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B469" s="1" t="s">
         <v>2633</v>
       </c>
@@ -43919,7 +43908,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="470" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B470" s="1" t="s">
         <v>1548</v>
       </c>
@@ -43988,7 +43977,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="471" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B471" t="s">
         <v>1548</v>
       </c>
@@ -44050,7 +44039,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="472" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B472" s="1" t="s">
         <v>759</v>
       </c>
@@ -44117,7 +44106,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="473" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B473" t="s">
         <v>759</v>
       </c>
@@ -44170,7 +44159,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="474" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B474" s="1" t="s">
         <v>759</v>
       </c>
@@ -44235,7 +44224,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="475" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B475" s="1" t="s">
         <v>2200</v>
       </c>
@@ -44304,7 +44293,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="476" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B476" t="s">
         <v>2200</v>
       </c>
@@ -44369,7 +44358,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="477" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B477" s="1" t="s">
         <v>2200</v>
       </c>
@@ -44434,7 +44423,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="478" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B478" s="1" t="s">
         <v>764</v>
       </c>
@@ -44497,7 +44486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="479" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B479" t="s">
         <v>764</v>
       </c>
@@ -44562,7 +44551,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="480" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B480" t="s">
         <v>764</v>
       </c>
@@ -44615,7 +44604,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="481" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B481" s="1" t="s">
         <v>764</v>
       </c>
@@ -44680,7 +44669,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="482" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B482" s="1" t="s">
         <v>2089</v>
       </c>
@@ -44749,7 +44738,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="483" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B483" s="1" t="s">
         <v>2089</v>
       </c>
@@ -44816,7 +44805,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="484" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B484" s="1" t="s">
         <v>377</v>
       </c>
@@ -44879,7 +44868,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="485" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B485" s="1" t="s">
         <v>377</v>
       </c>
@@ -44944,7 +44933,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="486" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B486" s="1" t="s">
         <v>2074</v>
       </c>
@@ -45013,7 +45002,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="487" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B487" t="s">
         <v>2074</v>
       </c>
@@ -45078,7 +45067,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="488" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B488" s="1" t="s">
         <v>2074</v>
       </c>
@@ -45145,7 +45134,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="489" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B489" t="s">
         <v>2074</v>
       </c>
@@ -45201,7 +45190,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="490" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B490" s="1" t="s">
         <v>383</v>
       </c>
@@ -45264,7 +45253,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="491" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B491" s="1" t="s">
         <v>383</v>
       </c>
@@ -45331,7 +45320,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="492" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B492" s="1" t="s">
         <v>383</v>
       </c>
@@ -45396,7 +45385,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="493" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B493" t="s">
         <v>2679</v>
       </c>
@@ -45461,7 +45450,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="494" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B494" s="1" t="s">
         <v>2679</v>
       </c>
@@ -45528,7 +45517,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="495" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B495" t="s">
         <v>2679</v>
       </c>
@@ -45590,7 +45579,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="496" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B496" s="1" t="s">
         <v>673</v>
       </c>
@@ -45653,7 +45642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="497" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B497" s="1" t="s">
         <v>673</v>
       </c>
@@ -45720,7 +45709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="498" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B498" s="1" t="s">
         <v>673</v>
       </c>
@@ -45785,7 +45774,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="499" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B499" s="1" t="s">
         <v>1606</v>
       </c>
@@ -45854,7 +45843,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="500" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B500" t="s">
         <v>1606</v>
       </c>
@@ -45919,7 +45908,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="501" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B501" t="s">
         <v>1606</v>
       </c>
@@ -45981,7 +45970,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="502" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B502" s="1" t="s">
         <v>360</v>
       </c>
@@ -46044,7 +46033,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="503" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B503" s="1" t="s">
         <v>360</v>
       </c>
@@ -46113,7 +46102,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="504" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B504" s="1" t="s">
         <v>360</v>
       </c>
@@ -46178,7 +46167,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="505" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B505" s="1" t="s">
         <v>2121</v>
       </c>
@@ -46247,7 +46236,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="506" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B506" t="s">
         <v>2121</v>
       </c>
@@ -46312,7 +46301,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="507" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B507" t="s">
         <v>2121</v>
       </c>
@@ -46374,7 +46363,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="508" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B508" s="1" t="s">
         <v>366</v>
       </c>
@@ -46437,7 +46426,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="509" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B509" s="1" t="s">
         <v>366</v>
       </c>
@@ -46504,7 +46493,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="510" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B510" t="s">
         <v>366</v>
       </c>
@@ -46566,7 +46555,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="511" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B511" s="1" t="s">
         <v>366</v>
       </c>
@@ -46631,7 +46620,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="512" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B512" s="1" t="s">
         <v>2116</v>
       </c>
@@ -46700,7 +46689,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="513" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B513" t="s">
         <v>2116</v>
       </c>
@@ -46765,7 +46754,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="514" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B514" s="1" t="s">
         <v>685</v>
       </c>
@@ -46832,7 +46821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="515" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B515" s="1" t="s">
         <v>685</v>
       </c>
@@ -46901,7 +46890,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="516" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B516" s="1" t="s">
         <v>685</v>
       </c>
@@ -46968,7 +46957,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="517" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B517" s="1" t="s">
         <v>685</v>
       </c>
@@ -47033,7 +47022,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="518" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B518" t="s">
         <v>2618</v>
       </c>
@@ -47098,7 +47087,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="519" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B519" t="s">
         <v>2618</v>
       </c>
@@ -47157,7 +47146,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="520" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B520" s="1" t="s">
         <v>389</v>
       </c>
@@ -47220,7 +47209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="521" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B521" s="1" t="s">
         <v>389</v>
       </c>
@@ -47287,7 +47276,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="522" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B522" s="1" t="s">
         <v>1793</v>
       </c>
@@ -47356,7 +47345,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="523" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B523" t="s">
         <v>1793</v>
       </c>
@@ -47421,7 +47410,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="524" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B524" t="s">
         <v>1793</v>
       </c>
@@ -47483,7 +47472,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="525" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B525" s="1" t="s">
         <v>1793</v>
       </c>
@@ -47552,7 +47541,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="526" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B526" s="1" t="s">
         <v>1118</v>
       </c>
@@ -47619,7 +47608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="527" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B527" s="1" t="s">
         <v>1118</v>
       </c>
@@ -47688,7 +47677,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="528" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B528" s="1" t="s">
         <v>2008</v>
       </c>
@@ -47757,7 +47746,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="529" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B529" t="s">
         <v>2008</v>
       </c>
@@ -47822,7 +47811,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="530" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B530" t="s">
         <v>2008</v>
       </c>
@@ -47884,7 +47873,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="531" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B531" s="1" t="s">
         <v>3619</v>
       </c>
@@ -47949,7 +47938,7 @@
       <c r="AA531" s="2"/>
       <c r="AB531" s="1"/>
     </row>
-    <row r="532" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B532" s="1" t="s">
         <v>1121</v>
       </c>
@@ -48016,7 +48005,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="533" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B533" s="1" t="s">
         <v>1121</v>
       </c>
@@ -48083,7 +48072,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="534" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B534" t="s">
         <v>1121</v>
       </c>
@@ -48142,7 +48131,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="535" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B535" s="1" t="s">
         <v>1522</v>
       </c>
@@ -48211,7 +48200,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="536" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B536" t="s">
         <v>1522</v>
       </c>
@@ -48276,7 +48265,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="537" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B537" s="1" t="s">
         <v>1522</v>
       </c>
@@ -48345,7 +48334,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="538" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B538" s="1" t="s">
         <v>1126</v>
       </c>
@@ -48412,7 +48401,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="539" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B539" s="1" t="s">
         <v>1126</v>
       </c>
@@ -48481,7 +48470,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="540" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B540" s="1" t="s">
         <v>1126</v>
       </c>
@@ -48548,7 +48537,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="541" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B541" t="s">
         <v>1126</v>
       </c>
@@ -48607,7 +48596,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="542" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B542" s="1" t="s">
         <v>3574</v>
       </c>
@@ -48676,7 +48665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="543" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B543" s="1" t="s">
         <v>1131</v>
       </c>
@@ -48743,7 +48732,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="544" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B544" s="1" t="s">
         <v>1131</v>
       </c>
@@ -48804,7 +48793,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="545" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B545" s="1" t="s">
         <v>1131</v>
       </c>
@@ -48871,7 +48860,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="546" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B546" t="s">
         <v>2473</v>
       </c>
@@ -48936,7 +48925,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="547" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B547" t="s">
         <v>2473</v>
       </c>
@@ -48998,7 +48987,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="548" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B548" s="1" t="s">
         <v>1136</v>
       </c>
@@ -49065,7 +49054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="549" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B549" s="1" t="s">
         <v>1136</v>
       </c>
@@ -49126,7 +49115,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="550" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B550" t="s">
         <v>2605</v>
       </c>
@@ -49191,7 +49180,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="551" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B551" s="1" t="s">
         <v>2605</v>
       </c>
@@ -49258,7 +49247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="552" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B552" t="s">
         <v>3265</v>
       </c>
@@ -49320,7 +49309,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="553" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B553" s="1" t="s">
         <v>1141</v>
       </c>
@@ -49387,7 +49376,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="554" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B554" s="1" t="s">
         <v>1141</v>
       </c>
@@ -49448,7 +49437,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="555" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B555" s="1" t="s">
         <v>1141</v>
       </c>
@@ -49515,7 +49504,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="556" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B556" t="s">
         <v>2482</v>
       </c>
@@ -49580,7 +49569,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="557" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B557" s="1" t="s">
         <v>691</v>
       </c>
@@ -49643,7 +49632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="558" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B558" s="1" t="s">
         <v>691</v>
       </c>
@@ -49704,7 +49693,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="559" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B559" t="s">
         <v>2427</v>
       </c>
@@ -49769,7 +49758,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="560" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B560" s="1" t="s">
         <v>2427</v>
       </c>
@@ -49838,7 +49827,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="561" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B561" s="1" t="s">
         <v>1086</v>
       </c>
@@ -49905,7 +49894,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="562" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B562" s="1" t="s">
         <v>1086</v>
       </c>
@@ -49966,7 +49955,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="563" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B563" t="s">
         <v>1086</v>
       </c>
@@ -50031,7 +50020,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="564" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B564" s="1" t="s">
         <v>1086</v>
       </c>
@@ -50094,7 +50083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="565" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B565" s="1" t="s">
         <v>3865</v>
       </c>
@@ -50163,7 +50152,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="566" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B566" s="1" t="s">
         <v>1092</v>
       </c>
@@ -50230,7 +50219,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="567" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B567" s="1" t="s">
         <v>1092</v>
       </c>
@@ -50291,7 +50280,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="568" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B568" s="1" t="s">
         <v>1092</v>
       </c>
@@ -50358,7 +50347,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="569" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B569" t="s">
         <v>2812</v>
       </c>
@@ -50423,7 +50412,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="570" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B570" s="1" t="s">
         <v>2812</v>
       </c>
@@ -50492,7 +50481,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="571" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B571" s="1" t="s">
         <v>422</v>
       </c>
@@ -50555,7 +50544,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="572" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B572" s="1" t="s">
         <v>422</v>
       </c>
@@ -50622,7 +50611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="573" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B573" s="1" t="s">
         <v>1836</v>
       </c>
@@ -50691,7 +50680,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="574" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B574" t="s">
         <v>1836</v>
       </c>
@@ -50756,7 +50745,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="575" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B575" s="1" t="s">
         <v>1836</v>
       </c>
@@ -50825,7 +50814,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="576" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B576" s="1" t="s">
         <v>354</v>
       </c>
@@ -50892,7 +50881,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="577" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B577" s="1" t="s">
         <v>354</v>
       </c>
@@ -50959,7 +50948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="578" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B578" s="1" t="s">
         <v>2031</v>
       </c>
@@ -51028,7 +51017,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="579" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B579" t="s">
         <v>2031</v>
       </c>
@@ -51093,7 +51082,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="580" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B580" s="1" t="s">
         <v>2031</v>
       </c>
@@ -51162,7 +51151,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="581" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B581" s="1" t="s">
         <v>667</v>
       </c>
@@ -51225,7 +51214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="582" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B582" s="1" t="s">
         <v>667</v>
       </c>
@@ -51292,7 +51281,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="583" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B583" s="1" t="s">
         <v>667</v>
       </c>
@@ -51359,7 +51348,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="584" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B584" s="1" t="s">
         <v>2125</v>
       </c>
@@ -51428,7 +51417,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="585" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B585" t="s">
         <v>2125</v>
       </c>
@@ -51493,7 +51482,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="586" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B586" s="1" t="s">
         <v>372</v>
       </c>
@@ -51560,7 +51549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="587" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B587" s="1" t="s">
         <v>372</v>
       </c>
@@ -51627,7 +51616,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="588" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B588" s="1" t="s">
         <v>372</v>
       </c>
@@ -51692,7 +51681,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="589" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B589" s="1" t="s">
         <v>2212</v>
       </c>
@@ -51761,7 +51750,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="590" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B590" s="1" t="s">
         <v>1097</v>
       </c>
@@ -51824,7 +51813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="591" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B591" s="1" t="s">
         <v>1097</v>
       </c>
@@ -51887,7 +51876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="592" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B592" s="1" t="s">
         <v>1097</v>
       </c>
@@ -51952,7 +51941,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="593" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B593" s="1" t="s">
         <v>1756</v>
       </c>
@@ -52021,7 +52010,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="594" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B594" t="s">
         <v>1756</v>
       </c>
@@ -52086,7 +52075,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="595" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B595" s="1" t="s">
         <v>1103</v>
       </c>
@@ -52153,7 +52142,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="596" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B596" s="1" t="s">
         <v>1103</v>
       </c>
@@ -52220,7 +52209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="597" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B597" s="1" t="s">
         <v>1903</v>
       </c>
@@ -52289,7 +52278,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="598" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B598" t="s">
         <v>1903</v>
       </c>
@@ -52354,7 +52343,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="599" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B599" s="1" t="s">
         <v>1108</v>
       </c>
@@ -52421,7 +52410,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="600" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B600" s="1" t="s">
         <v>1108</v>
       </c>
@@ -52490,7 +52479,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="601" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B601" s="1" t="s">
         <v>2217</v>
       </c>
@@ -52559,7 +52548,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="602" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B602" t="s">
         <v>2217</v>
       </c>
@@ -52624,7 +52613,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="603" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B603" s="1" t="s">
         <v>401</v>
       </c>
@@ -52687,7 +52676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="604" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B604" s="1" t="s">
         <v>401</v>
       </c>
@@ -52754,7 +52743,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="605" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B605" s="1" t="s">
         <v>1820</v>
       </c>
@@ -52823,7 +52812,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="606" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B606" s="1" t="s">
         <v>1820</v>
       </c>
@@ -52892,7 +52881,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="607" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B607" s="1" t="s">
         <v>644</v>
       </c>
@@ -52955,7 +52944,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="608" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B608" t="s">
         <v>644</v>
       </c>
@@ -53017,7 +53006,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="609" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B609" s="1" t="s">
         <v>644</v>
       </c>
@@ -53086,7 +53075,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="610" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B610" s="1" t="s">
         <v>1558</v>
       </c>
@@ -53155,7 +53144,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="611" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B611" s="1" t="s">
         <v>1558</v>
       </c>
@@ -53224,7 +53213,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="612" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B612" s="1" t="s">
         <v>1074</v>
       </c>
@@ -53287,7 +53276,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="613" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B613" s="1" t="s">
         <v>1074</v>
       </c>
@@ -53354,7 +53343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="614" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B614" t="s">
         <v>2562</v>
       </c>
@@ -53419,7 +53408,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="615" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B615" s="1" t="s">
         <v>1080</v>
       </c>
@@ -53482,7 +53471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="616" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B616" s="1" t="s">
         <v>1080</v>
       </c>
@@ -53543,7 +53532,7 @@
         <v>2311</v>
       </c>
     </row>
-    <row r="617" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B617" s="1" t="s">
         <v>1080</v>
       </c>
@@ -53610,7 +53599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="618" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B618" s="1" t="s">
         <v>1080</v>
       </c>
@@ -53677,7 +53666,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="619" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B619" t="s">
         <v>2364</v>
       </c>
@@ -53742,7 +53731,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="620" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B620" s="1" t="s">
         <v>650</v>
       </c>
@@ -53805,7 +53794,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="621" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B621" t="s">
         <v>650</v>
       </c>
@@ -53870,7 +53859,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="622" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B622" s="1" t="s">
         <v>650</v>
       </c>
@@ -53937,7 +53926,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="623" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B623" s="1" t="s">
         <v>650</v>
       </c>
@@ -54002,7 +53991,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="624" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B624" s="1" t="s">
         <v>1767</v>
       </c>
@@ -54071,7 +54060,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="625" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B625" s="1" t="s">
         <v>656</v>
       </c>
@@ -54134,7 +54123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="626" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B626" s="1" t="s">
         <v>656</v>
       </c>
@@ -54201,7 +54190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="627" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B627" s="1" t="s">
         <v>656</v>
       </c>
@@ -54266,7 +54255,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="628" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B628" s="1" t="s">
         <v>1841</v>
       </c>
@@ -54335,7 +54324,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="629" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B629" t="s">
         <v>1841</v>
       </c>
@@ -54400,7 +54389,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="630" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B630" s="1" t="s">
         <v>1066</v>
       </c>
@@ -54467,7 +54456,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="631" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B631" s="1" t="s">
         <v>1066</v>
       </c>
@@ -54536,7 +54525,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="632" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B632" s="1" t="s">
         <v>1066</v>
       </c>
@@ -54603,7 +54592,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="633" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B633" s="1" t="s">
         <v>1066</v>
       </c>
@@ -54672,7 +54661,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="634" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B634" t="s">
         <v>2418</v>
       </c>
@@ -54737,7 +54726,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="635" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B635" s="1" t="s">
         <v>1071</v>
       </c>
@@ -54804,7 +54793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="636" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B636" s="1" t="s">
         <v>1071</v>
       </c>
@@ -54873,7 +54862,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="637" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B637" s="1" t="s">
         <v>1071</v>
       </c>
@@ -54940,7 +54929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="638" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B638" s="1" t="s">
         <v>1071</v>
       </c>
@@ -55007,7 +54996,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="639" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B639" s="1" t="s">
         <v>319</v>
       </c>
@@ -55074,7 +55063,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="640" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B640" s="1" t="s">
         <v>319</v>
       </c>
@@ -55141,7 +55130,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="641" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B641" s="1" t="s">
         <v>2058</v>
       </c>
@@ -55210,7 +55199,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="642" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B642" t="s">
         <v>2058</v>
       </c>
@@ -55275,7 +55264,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="643" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B643" s="1" t="s">
         <v>2058</v>
       </c>
@@ -55344,7 +55333,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="644" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B644" s="1" t="s">
         <v>697</v>
       </c>
@@ -55407,7 +55396,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="645" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B645" s="1" t="s">
         <v>697</v>
       </c>
@@ -55474,7 +55463,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="646" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B646" s="1" t="s">
         <v>1881</v>
       </c>
@@ -55543,7 +55532,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="647" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B647" t="s">
         <v>1881</v>
       </c>
@@ -55608,7 +55597,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="648" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B648" s="1" t="s">
         <v>1881</v>
       </c>
@@ -55673,7 +55662,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="649" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B649" s="1" t="s">
         <v>1050</v>
       </c>
@@ -55736,7 +55725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="650" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B650" s="1" t="s">
         <v>2026</v>
       </c>
@@ -55805,7 +55794,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="651" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B651" t="s">
         <v>2026</v>
       </c>
@@ -55870,7 +55859,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="652" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B652" s="1" t="s">
         <v>395</v>
       </c>
@@ -55933,7 +55922,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="653" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B653" t="s">
         <v>2786</v>
       </c>
@@ -55998,7 +55987,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="654" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B654" s="1" t="s">
         <v>2786</v>
       </c>
@@ -56063,7 +56052,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="655" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B655" s="1" t="s">
         <v>662</v>
       </c>
@@ -56130,7 +56119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="656" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B656" s="1" t="s">
         <v>2047</v>
       </c>
@@ -56199,7 +56188,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="657" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B657" t="s">
         <v>2047</v>
       </c>
@@ -56264,7 +56253,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="658" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B658" s="1" t="s">
         <v>3602</v>
       </c>
@@ -56329,7 +56318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="659" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B659" s="1" t="s">
         <v>1056</v>
       </c>
@@ -56396,7 +56385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="660" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B660" s="1" t="s">
         <v>2094</v>
       </c>
@@ -56465,7 +56454,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="661" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B661" t="s">
         <v>2094</v>
       </c>
@@ -56530,7 +56519,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="662" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B662" s="1" t="s">
         <v>3682</v>
       </c>
@@ -56599,7 +56588,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="663" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B663" s="1" t="s">
         <v>1061</v>
       </c>
@@ -56666,7 +56655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="664" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B664" s="1" t="s">
         <v>1578</v>
       </c>
@@ -56735,7 +56724,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="665" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B665" s="1" t="s">
         <v>417</v>
       </c>
@@ -56802,7 +56791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="666" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B666" t="s">
         <v>417</v>
       </c>
@@ -56867,7 +56856,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="667" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B667" s="1" t="s">
         <v>1978</v>
       </c>
@@ -56936,7 +56925,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="668" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B668" s="1" t="s">
         <v>955</v>
       </c>
@@ -57003,7 +56992,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="669" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B669" s="1" t="s">
         <v>1993</v>
       </c>
@@ -57072,7 +57061,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="670" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B670" s="1" t="s">
         <v>1993</v>
       </c>
@@ -57139,7 +57128,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="671" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B671" s="1" t="s">
         <v>306</v>
       </c>
@@ -57206,7 +57195,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="672" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B672" s="1" t="s">
         <v>306</v>
       </c>
@@ -57275,7 +57264,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="673" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B673" t="s">
         <v>2445</v>
       </c>
@@ -57340,7 +57329,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="674" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B674" s="1" t="s">
         <v>311</v>
       </c>
@@ -57407,7 +57396,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="675" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B675" s="1" t="s">
         <v>1972</v>
       </c>
@@ -57476,7 +57465,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="676" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B676" t="s">
         <v>1972</v>
       </c>
@@ -57541,7 +57530,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="677" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B677" s="1" t="s">
         <v>3639</v>
       </c>
@@ -57610,7 +57599,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="678" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B678" s="1" t="s">
         <v>960</v>
       </c>
@@ -57677,7 +57666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="679" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B679" s="1" t="s">
         <v>1788</v>
       </c>
@@ -57746,7 +57735,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="680" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B680" t="s">
         <v>1788</v>
       </c>
@@ -57811,7 +57800,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="681" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B681" s="1" t="s">
         <v>1788</v>
       </c>
@@ -57880,7 +57869,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="682" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B682" s="1" t="s">
         <v>965</v>
       </c>
@@ -57947,7 +57936,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="683" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B683" s="1" t="s">
         <v>965</v>
       </c>
@@ -58014,7 +58003,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="684" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B684" t="s">
         <v>2729</v>
       </c>
@@ -58079,7 +58068,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="685" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B685" s="1" t="s">
         <v>970</v>
       </c>
@@ -58146,7 +58135,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="686" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B686" s="1" t="s">
         <v>970</v>
       </c>
@@ -58215,7 +58204,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="687" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B687" s="1" t="s">
         <v>970</v>
       </c>
@@ -58284,7 +58273,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="688" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B688" s="1" t="s">
         <v>975</v>
       </c>
@@ -58351,7 +58340,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="689" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B689" s="1" t="s">
         <v>975</v>
       </c>
@@ -58418,7 +58407,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="690" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B690" s="1" t="s">
         <v>1673</v>
       </c>
@@ -58487,7 +58476,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="691" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B691" t="s">
         <v>1673</v>
       </c>
@@ -58552,7 +58541,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="692" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B692" s="1" t="s">
         <v>980</v>
       </c>
@@ -58619,7 +58608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="693" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B693" s="1" t="s">
         <v>2174</v>
       </c>
@@ -58688,7 +58677,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="694" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B694" t="s">
         <v>2413</v>
       </c>
@@ -58753,7 +58742,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="695" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B695" s="1" t="s">
         <v>2413</v>
       </c>
@@ -58822,7 +58811,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="696" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B696" s="1" t="s">
         <v>703</v>
       </c>
@@ -58889,7 +58878,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="697" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B697" t="s">
         <v>703</v>
       </c>
@@ -58951,7 +58940,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="698" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B698" s="1" t="s">
         <v>1825</v>
       </c>
@@ -59020,7 +59009,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="699" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B699" s="1" t="s">
         <v>3717</v>
       </c>
@@ -59089,7 +59078,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="700" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B700" s="1" t="s">
         <v>412</v>
       </c>
@@ -59156,7 +59145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="701" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B701" t="s">
         <v>412</v>
       </c>
@@ -59218,7 +59207,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="702" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B702" s="1" t="s">
         <v>412</v>
       </c>
@@ -59287,7 +59276,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="703" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B703" s="1" t="s">
         <v>934</v>
       </c>
@@ -59354,7 +59343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="704" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B704" t="s">
         <v>934</v>
       </c>
@@ -59419,7 +59408,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="705" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B705" s="1" t="s">
         <v>2111</v>
       </c>
@@ -59488,7 +59477,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="706" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B706" s="1" t="s">
         <v>2111</v>
       </c>
@@ -59553,7 +59542,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="707" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B707" s="1" t="s">
         <v>939</v>
       </c>
@@ -59622,7 +59611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="708" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B708" s="1" t="s">
         <v>939</v>
       </c>
@@ -59689,7 +59678,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="709" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B709" t="s">
         <v>939</v>
       </c>
@@ -59754,7 +59743,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="710" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B710" s="1" t="s">
         <v>4005</v>
       </c>
@@ -59823,7 +59812,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="711" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B711" s="1" t="s">
         <v>325</v>
       </c>
@@ -59890,7 +59879,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="712" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B712" s="1" t="s">
         <v>3707</v>
       </c>
@@ -59955,7 +59944,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="713" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B713" s="1" t="s">
         <v>336</v>
       </c>
@@ -60022,7 +60011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="714" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B714" s="1" t="s">
         <v>2179</v>
       </c>
@@ -60091,7 +60080,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="715" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B715" s="1" t="s">
         <v>2179</v>
       </c>
@@ -60160,7 +60149,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="716" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B716" s="1" t="s">
         <v>708</v>
       </c>
@@ -60227,7 +60216,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="717" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B717" s="1" t="s">
         <v>2069</v>
       </c>
@@ -60296,7 +60285,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="718" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B718" s="1" t="s">
         <v>2069</v>
       </c>
@@ -60365,7 +60354,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="719" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B719" s="1" t="s">
         <v>929</v>
       </c>
@@ -60432,7 +60421,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="720" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B720" s="1" t="s">
         <v>341</v>
       </c>
@@ -60499,7 +60488,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="721" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B721" s="1" t="s">
         <v>1639</v>
       </c>
@@ -60568,7 +60557,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="722" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B722" s="1" t="s">
         <v>945</v>
       </c>
@@ -60635,7 +60624,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="723" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B723" s="1" t="s">
         <v>945</v>
       </c>
@@ -60696,7 +60685,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="724" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B724" s="1" t="s">
         <v>3856</v>
       </c>
@@ -60765,7 +60754,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="725" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B725" s="1" t="s">
         <v>950</v>
       </c>
@@ -60832,7 +60821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="726" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B726" s="1" t="s">
         <v>950</v>
       </c>
@@ -60893,7 +60882,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="727" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B727" s="1" t="s">
         <v>344</v>
       </c>
@@ -60960,7 +60949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="728" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B728" s="1" t="s">
         <v>344</v>
       </c>
@@ -61021,7 +61010,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="729" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B729" s="1" t="s">
         <v>3644</v>
       </c>
@@ -61088,7 +61077,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="730" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B730" s="1" t="s">
         <v>993</v>
       </c>
@@ -61155,7 +61144,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="731" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B731" s="1" t="s">
         <v>993</v>
       </c>
@@ -61216,7 +61205,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="732" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B732" s="1" t="s">
         <v>3834</v>
       </c>
@@ -61285,7 +61274,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="733" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B733" s="1" t="s">
         <v>349</v>
       </c>
@@ -61352,7 +61341,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="734" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B734" s="1" t="s">
         <v>349</v>
       </c>
@@ -61413,7 +61402,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="735" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B735" s="1" t="s">
         <v>3587</v>
       </c>
@@ -61482,7 +61471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="736" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B736" s="1" t="s">
         <v>314</v>
       </c>
@@ -61549,7 +61538,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="737" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B737" s="1" t="s">
         <v>314</v>
       </c>
@@ -61616,7 +61605,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="738" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B738" s="1" t="s">
         <v>2157</v>
       </c>
@@ -61685,7 +61674,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="739" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B739" s="1" t="s">
         <v>998</v>
       </c>
@@ -61752,7 +61741,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="740" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B740" s="1" t="s">
         <v>1455</v>
       </c>
@@ -61819,7 +61808,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="741" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B741" s="1" t="s">
         <v>1455</v>
       </c>
@@ -61888,7 +61877,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="742" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B742" s="1" t="s">
         <v>407</v>
       </c>
@@ -61955,7 +61944,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="743" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B743" s="1" t="s">
         <v>2063</v>
       </c>
@@ -62024,7 +62013,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="744" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B744" s="1" t="s">
         <v>2063</v>
       </c>
@@ -62089,7 +62078,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="745" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B745" s="1" t="s">
         <v>983</v>
       </c>
@@ -62156,7 +62145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="746" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B746" s="1" t="s">
         <v>1898</v>
       </c>
@@ -62225,7 +62214,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="747" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B747" s="1" t="s">
         <v>1898</v>
       </c>
@@ -62294,7 +62283,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="748" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B748" s="1" t="s">
         <v>1213</v>
       </c>
@@ -62361,7 +62350,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="749" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B749" s="1" t="s">
         <v>1831</v>
       </c>
@@ -62430,7 +62419,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="750" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B750" s="1" t="s">
         <v>1831</v>
       </c>
@@ -62499,7 +62488,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="751" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B751" s="1" t="s">
         <v>988</v>
       </c>
@@ -62566,7 +62555,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="752" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B752" s="1" t="s">
         <v>1809</v>
       </c>
@@ -62635,7 +62624,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="753" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B753" s="1" t="s">
         <v>1809</v>
       </c>
@@ -62704,7 +62693,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="754" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B754" s="1" t="s">
         <v>291</v>
       </c>
@@ -62771,7 +62760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="755" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B755" s="1" t="s">
         <v>2195</v>
       </c>
@@ -62840,7 +62829,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="756" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B756" s="1" t="s">
         <v>3597</v>
       </c>
@@ -62909,7 +62898,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="757" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B757" s="1" t="s">
         <v>1163</v>
       </c>
@@ -62978,7 +62967,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="758" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B758" s="1" t="s">
         <v>1163</v>
       </c>
@@ -63047,7 +63036,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="759" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B759" s="1" t="s">
         <v>3582</v>
       </c>
@@ -63116,7 +63105,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="760" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B760" s="1" t="s">
         <v>286</v>
       </c>
@@ -63183,7 +63172,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="761" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B761" s="1" t="s">
         <v>286</v>
       </c>
@@ -63252,7 +63241,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="762" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B762" s="1" t="s">
         <v>3748</v>
       </c>
@@ -63317,7 +63306,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="763" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B763" s="1" t="s">
         <v>1029</v>
       </c>
@@ -63384,7 +63373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="764" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B764" s="1" t="s">
         <v>1029</v>
       </c>
@@ -63453,7 +63442,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="765" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B765" s="1" t="s">
         <v>3702</v>
       </c>
@@ -63522,7 +63511,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="766" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B766" s="1" t="s">
         <v>1034</v>
       </c>
@@ -63591,7 +63580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="767" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B767" s="1" t="s">
         <v>1034</v>
       </c>
@@ -63660,7 +63649,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="768" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B768" s="1" t="s">
         <v>1034</v>
       </c>
@@ -63723,7 +63712,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="769" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B769" s="1" t="s">
         <v>1040</v>
       </c>
@@ -63790,7 +63779,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="770" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B770" s="1" t="s">
         <v>1040</v>
       </c>
@@ -63859,7 +63848,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="771" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B771" s="1" t="s">
         <v>3559</v>
       </c>
@@ -63928,7 +63917,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="772" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B772" s="1" t="s">
         <v>1045</v>
       </c>
@@ -63995,7 +63984,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="773" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B773" s="1" t="s">
         <v>1045</v>
       </c>
@@ -64056,7 +64045,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="774" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B774" s="1" t="s">
         <v>1045</v>
       </c>
@@ -64123,7 +64112,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="775" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B775" s="1" t="s">
         <v>301</v>
       </c>
@@ -64190,7 +64179,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="776" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B776" s="1" t="s">
         <v>3542</v>
       </c>
@@ -64255,7 +64244,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="777" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B777" s="1" t="s">
         <v>1940</v>
       </c>
@@ -64324,7 +64313,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="778" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B778" s="1" t="s">
         <v>1003</v>
       </c>
@@ -64391,7 +64380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="779" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B779" s="1" t="s">
         <v>1003</v>
       </c>
@@ -64452,7 +64441,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="780" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B780" s="1" t="s">
         <v>1008</v>
       </c>
@@ -64519,7 +64508,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="781" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B781" s="1" t="s">
         <v>2184</v>
       </c>
@@ -64588,7 +64577,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="782" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B782" s="1" t="s">
         <v>2184</v>
       </c>
@@ -64653,7 +64642,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="783" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B783" s="1" t="s">
         <v>1013</v>
       </c>
@@ -64720,7 +64709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="784" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B784" s="1" t="s">
         <v>2099</v>
       </c>
@@ -64789,7 +64778,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="785" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B785" s="1" t="s">
         <v>1018</v>
       </c>
@@ -64858,7 +64847,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="786" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B786" s="1" t="s">
         <v>2135</v>
       </c>
@@ -64927,7 +64916,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="787" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B787" s="1" t="s">
         <v>1024</v>
       </c>
@@ -64994,7 +64983,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="788" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B788" s="1" t="s">
         <v>1512</v>
       </c>
@@ -65063,7 +65052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="789" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B789" s="1" t="s">
         <v>1512</v>
       </c>
@@ -65128,7 +65117,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="790" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B790" s="1" t="s">
         <v>274</v>
       </c>
@@ -65197,7 +65186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="791" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B791" s="1" t="s">
         <v>274</v>
       </c>
@@ -65264,7 +65253,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="792" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B792" s="1" t="s">
         <v>1783</v>
       </c>
@@ -65333,7 +65322,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="793" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B793" s="1" t="s">
         <v>1146</v>
       </c>
@@ -65400,7 +65389,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="794" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B794" s="1" t="s">
         <v>1146</v>
       </c>
@@ -65471,7 +65460,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="795" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B795" s="1" t="s">
         <v>2130</v>
       </c>
@@ -65540,7 +65529,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="796" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B796" s="1" t="s">
         <v>1151</v>
       </c>
@@ -65607,7 +65596,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="797" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B797" s="1" t="s">
         <v>1151</v>
       </c>
@@ -65676,7 +65665,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="798" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B798" s="1" t="s">
         <v>2223</v>
       </c>
@@ -65745,7 +65734,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="799" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B799" s="1" t="s">
         <v>1154</v>
       </c>
@@ -65812,7 +65801,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="800" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B800" s="1" t="s">
         <v>1154</v>
       </c>
@@ -65881,7 +65870,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="801" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B801" s="1" t="s">
         <v>1983</v>
       </c>
@@ -65950,7 +65939,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="802" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B802" s="1" t="s">
         <v>1157</v>
       </c>
@@ -66017,7 +66006,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="803" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B803" s="1" t="s">
         <v>2151</v>
       </c>
@@ -66086,7 +66075,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="804" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B804" s="1" t="s">
         <v>2151</v>
       </c>
@@ -66155,7 +66144,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="805" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B805" s="1" t="s">
         <v>1160</v>
       </c>
@@ -66222,7 +66211,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="806" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B806" s="1" t="s">
         <v>3564</v>
       </c>
@@ -66291,7 +66280,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="807" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B807" s="1" t="s">
         <v>246</v>
       </c>
@@ -66354,7 +66343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="808" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B808" s="1" t="s">
         <v>3624</v>
       </c>
@@ -66423,7 +66412,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="809" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B809" s="1" t="s">
         <v>252</v>
       </c>
@@ -66486,7 +66475,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="810" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B810" s="1" t="s">
         <v>252</v>
       </c>
@@ -66553,7 +66542,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="811" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B811" s="1" t="s">
         <v>268</v>
       </c>
@@ -66616,7 +66605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="812" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B812" s="1" t="s">
         <v>268</v>
       </c>
@@ -66683,7 +66672,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="813" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B813" s="1" t="s">
         <v>2252</v>
       </c>
@@ -66750,7 +66739,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="814" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B814" s="1" t="s">
         <v>494</v>
       </c>
@@ -66813,7 +66802,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="815" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B815" s="1" t="s">
         <v>1869</v>
       </c>
@@ -66882,7 +66871,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="816" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B816" s="1" t="s">
         <v>1869</v>
       </c>
@@ -66951,7 +66940,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="817" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B817" s="1" t="s">
         <v>500</v>
       </c>
@@ -67014,7 +67003,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="818" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B818" s="1" t="s">
         <v>1886</v>
       </c>
@@ -67083,7 +67072,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="819" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B819" s="1" t="s">
         <v>506</v>
       </c>
@@ -67146,7 +67135,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="820" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B820" s="1" t="s">
         <v>1988</v>
       </c>
@@ -67215,7 +67204,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="821" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B821" s="1" t="s">
         <v>330</v>
       </c>
@@ -67278,7 +67267,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="822" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B822" s="1" t="s">
         <v>1945</v>
       </c>
@@ -67347,7 +67336,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="823" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B823" s="1" t="s">
         <v>488</v>
       </c>
@@ -67410,7 +67399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="824" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B824" s="1" t="s">
         <v>488</v>
       </c>
@@ -67479,7 +67468,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="825" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B825" s="1" t="s">
         <v>280</v>
       </c>
@@ -67542,7 +67531,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="826" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B826" s="1" t="s">
         <v>476</v>
       </c>
@@ -67605,7 +67594,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="827" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B827" s="1" t="s">
         <v>1695</v>
       </c>
@@ -67674,7 +67663,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="828" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B828" s="1" t="s">
         <v>482</v>
       </c>
@@ -67737,7 +67726,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="829" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B829" s="1" t="s">
         <v>482</v>
       </c>
@@ -67804,7 +67793,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="830" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B830" s="1" t="s">
         <v>458</v>
       </c>
@@ -67867,7 +67856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="831" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B831" s="1" t="s">
         <v>1645</v>
       </c>
@@ -67936,7 +67925,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="832" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B832" s="1" t="s">
         <v>464</v>
       </c>
@@ -67999,7 +67988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="833" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B833" s="1" t="s">
         <v>1460</v>
       </c>
@@ -68068,7 +68057,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="834" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B834" s="1" t="s">
         <v>470</v>
       </c>
@@ -68131,7 +68120,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="835" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B835" s="1" t="s">
         <v>470</v>
       </c>
@@ -68192,7 +68181,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="836" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B836" s="1" t="s">
         <v>223</v>
       </c>
@@ -68255,7 +68244,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="837" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B837" s="1" t="s">
         <v>1892</v>
       </c>
@@ -68324,7 +68313,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="838" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B838" s="1" t="s">
         <v>229</v>
       </c>
@@ -68391,7 +68380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="839" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B839" s="1" t="s">
         <v>229</v>
       </c>
@@ -68452,7 +68441,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="840" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B840" s="1" t="s">
         <v>207</v>
       </c>
@@ -68519,7 +68508,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="841" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B841" s="1" t="s">
         <v>1734</v>
       </c>
@@ -68588,7 +68577,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="842" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B842" s="1" t="s">
         <v>1175</v>
       </c>
@@ -68655,7 +68644,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="843" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B843" s="1" t="s">
         <v>1175</v>
       </c>
@@ -68724,7 +68713,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="844" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B844" s="1" t="s">
         <v>1180</v>
       </c>
@@ -68791,7 +68780,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="845" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B845" s="1" t="s">
         <v>1701</v>
       </c>
@@ -68860,7 +68849,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="846" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B846" s="1" t="s">
         <v>1186</v>
       </c>
@@ -68927,7 +68916,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="847" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B847" s="1" t="s">
         <v>1186</v>
       </c>
@@ -68996,7 +68985,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="848" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B848" s="1" t="s">
         <v>296</v>
       </c>
@@ -69063,7 +69052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="849" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B849" s="1" t="s">
         <v>1527</v>
       </c>
@@ -69132,7 +69121,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="850" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B850" s="1" t="s">
         <v>212</v>
       </c>
@@ -69195,7 +69184,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="851" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B851" s="1" t="s">
         <v>2003</v>
       </c>
@@ -69262,7 +69251,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="852" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B852" s="1" t="s">
         <v>218</v>
       </c>
@@ -69329,7 +69318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="853" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B853" s="1" t="s">
         <v>258</v>
       </c>
@@ -69396,7 +69385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="854" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B854" s="1" t="s">
         <v>1739</v>
       </c>
@@ -69465,7 +69454,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="855" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B855" s="1" t="s">
         <v>1169</v>
       </c>
@@ -69528,7 +69517,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="856" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B856" s="1" t="s">
         <v>1908</v>
       </c>
@@ -69597,7 +69586,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="857" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B857" s="1" t="s">
         <v>191</v>
       </c>
@@ -69664,7 +69653,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="858" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B858" s="1" t="s">
         <v>191</v>
       </c>
@@ -69733,7 +69722,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="859" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B859" s="1" t="s">
         <v>160</v>
       </c>
@@ -69796,7 +69785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="860" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B860" s="1" t="s">
         <v>1706</v>
       </c>
@@ -69865,7 +69854,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="861" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B861" s="1" t="s">
         <v>185</v>
       </c>
@@ -69934,7 +69923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="862" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B862" s="1" t="s">
         <v>1634</v>
       </c>
@@ -70003,7 +69992,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="863" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B863" s="1" t="s">
         <v>240</v>
       </c>
@@ -70066,7 +70055,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="864" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B864" s="1" t="s">
         <v>240</v>
       </c>
@@ -70129,7 +70118,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="865" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B865" s="1" t="s">
         <v>202</v>
       </c>
@@ -70196,7 +70185,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="866" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B866" s="1" t="s">
         <v>143</v>
       </c>
@@ -70259,7 +70248,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="867" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B867" s="1" t="s">
         <v>1690</v>
       </c>
@@ -70328,7 +70317,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="868" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B868" s="1" t="s">
         <v>155</v>
       </c>
@@ -70395,7 +70384,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="869" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B869" s="1" t="s">
         <v>2020</v>
       </c>
@@ -70464,7 +70453,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="870" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B870" s="1" t="s">
         <v>263</v>
       </c>
@@ -70531,7 +70520,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="871" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B871" s="1" t="s">
         <v>2140</v>
       </c>
@@ -70600,7 +70589,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="872" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B872" s="1" t="s">
         <v>196</v>
       </c>
@@ -70663,7 +70652,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="873" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B873" s="1" t="s">
         <v>2190</v>
       </c>
@@ -70732,7 +70721,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="874" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B874" s="1" t="s">
         <v>137</v>
       </c>
@@ -70801,7 +70790,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="875" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B875" s="1" t="s">
         <v>2162</v>
       </c>
@@ -70870,7 +70859,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="876" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B876" s="1" t="s">
         <v>172</v>
       </c>
@@ -70937,7 +70926,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="877" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B877" s="1" t="s">
         <v>1651</v>
       </c>
@@ -71006,7 +70995,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="878" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B878" s="1" t="s">
         <v>166</v>
       </c>
@@ -71073,7 +71062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="879" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B879" s="1" t="s">
         <v>1778</v>
       </c>
@@ -71140,7 +71129,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="880" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B880" s="1" t="s">
         <v>133</v>
       </c>
@@ -71209,7 +71198,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="881" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B881" s="1" t="s">
         <v>1679</v>
       </c>
@@ -71276,7 +71265,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="882" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B882" s="1" t="s">
         <v>149</v>
       </c>
@@ -71345,7 +71334,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="883" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B883" s="1" t="s">
         <v>175</v>
       </c>
@@ -71414,7 +71403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="884" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B884" s="1" t="s">
         <v>1623</v>
       </c>
@@ -71483,7 +71472,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="885" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B885" s="1" t="s">
         <v>181</v>
       </c>
@@ -71552,7 +71541,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="886" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B886" s="1" t="s">
         <v>1583</v>
       </c>
@@ -71621,7 +71610,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="887" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B887" s="1" t="s">
         <v>127</v>
       </c>
@@ -71684,7 +71673,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="888" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B888" s="1" t="s">
         <v>1628</v>
       </c>
@@ -71753,7 +71742,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="889" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B889" s="1" t="s">
         <v>234</v>
       </c>
@@ -71816,7 +71805,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="890" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B890" s="1" t="s">
         <v>234</v>
       </c>
@@ -71883,7 +71872,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="891" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B891" s="1" t="s">
         <v>104</v>
       </c>
@@ -71946,7 +71935,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="892" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B892" s="1" t="s">
         <v>104</v>
       </c>
@@ -72013,7 +72002,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="893" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B893" s="1" t="s">
         <v>117</v>
       </c>
@@ -72080,7 +72069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="894" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B894" s="1" t="s">
         <v>117</v>
       </c>
@@ -72143,7 +72132,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="895" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B895" s="1" t="s">
         <v>122</v>
       </c>
@@ -72210,7 +72199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="896" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B896" s="1" t="s">
         <v>1998</v>
       </c>
@@ -72279,7 +72268,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="897" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B897" s="1" t="s">
         <v>99</v>
       </c>
@@ -72346,7 +72335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="898" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B898" s="1" t="s">
         <v>2042</v>
       </c>
@@ -72415,7 +72404,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="899" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B899" s="1" t="s">
         <v>89</v>
       </c>
@@ -72482,7 +72471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="900" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B900" s="1" t="s">
         <v>89</v>
       </c>
@@ -72549,7 +72538,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="901" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B901" s="1" t="s">
         <v>94</v>
       </c>
@@ -72616,7 +72605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="902" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B902" s="1" t="s">
         <v>1492</v>
       </c>
@@ -72683,7 +72672,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="903" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B903" s="1" t="s">
         <v>2206</v>
       </c>
@@ -72752,7 +72741,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="904" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B904" s="1" t="s">
         <v>83</v>
       </c>
@@ -72815,7 +72804,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="905" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B905" s="1" t="s">
         <v>1924</v>
       </c>
@@ -72882,7 +72871,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="906" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B906" s="1" t="s">
         <v>1466</v>
       </c>
@@ -72951,7 +72940,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="907" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B907" s="1" t="s">
         <v>110</v>
       </c>
@@ -73020,7 +73009,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="908" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B908" s="1" t="s">
         <v>77</v>
       </c>
@@ -73083,7 +73072,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="909" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B909" s="1" t="s">
         <v>1814</v>
       </c>
@@ -73152,7 +73141,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="910" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B910" s="1" t="s">
         <v>34</v>
       </c>
@@ -73219,7 +73208,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="911" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B911" s="1" t="s">
         <v>1600</v>
       </c>
@@ -73288,7 +73277,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="912" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B912" s="1" t="s">
         <v>39</v>
       </c>
@@ -73355,7 +73344,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="913" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B913" s="1" t="s">
         <v>1722</v>
       </c>
@@ -73424,7 +73413,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="914" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B914" s="1" t="s">
         <v>44</v>
       </c>
@@ -73487,7 +73476,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="915" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B915" s="1" t="s">
         <v>1667</v>
       </c>
@@ -73556,7 +73545,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="916" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B916" s="1" t="s">
         <v>66</v>
       </c>
@@ -73619,7 +73608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="917" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B917" s="1" t="s">
         <v>1773</v>
       </c>
@@ -73688,7 +73677,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="918" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B918" s="1" t="s">
         <v>72</v>
       </c>
@@ -73755,7 +73744,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="919" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B919" s="1" t="s">
         <v>1745</v>
       </c>
@@ -73824,7 +73813,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="920" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B920" s="1" t="s">
         <v>56</v>
       </c>
@@ -73891,7 +73880,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="921" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B921" s="1" t="s">
         <v>1728</v>
       </c>
@@ -73960,7 +73949,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="922" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B922" s="1" t="s">
         <v>61</v>
       </c>
@@ -74027,7 +74016,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="923" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B923" s="1" t="s">
         <v>1542</v>
       </c>
@@ -74096,7 +74085,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="924" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B924" s="1" t="s">
         <v>50</v>
       </c>
@@ -74159,7 +74148,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="925" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B925" s="1" t="s">
         <v>1574</v>
       </c>
@@ -74226,7 +74215,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="926" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B926" s="1" t="s">
         <v>20</v>
       </c>
@@ -74293,7 +74282,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="927" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B927" s="1" t="s">
         <v>1685</v>
       </c>
@@ -74362,7 +74351,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="928" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B928" s="1" t="s">
         <v>25</v>
       </c>
@@ -74429,7 +74418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="929" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B929" s="1" t="s">
         <v>1798</v>
       </c>
@@ -74498,7 +74487,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="930" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B930" s="1" t="s">
         <v>28</v>
       </c>
@@ -74561,7 +74550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="931" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B931" s="1" t="s">
         <v>1612</v>
       </c>
@@ -74630,7 +74619,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="932" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B932" s="1" t="s">
         <v>0</v>
       </c>
@@ -74693,7 +74682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="933" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B933" s="1" t="s">
         <v>1594</v>
       </c>
@@ -74762,7 +74751,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="934" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B934" s="1" t="s">
         <v>13</v>
       </c>
@@ -74829,7 +74818,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="935" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B935" s="1" t="s">
         <v>1476</v>
       </c>
@@ -74898,7 +74887,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="936" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B936" s="1" t="s">
         <v>1617</v>
       </c>
@@ -74967,7 +74956,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="937" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B937" s="1" t="s">
         <v>1588</v>
       </c>
@@ -75036,7 +75025,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="938" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B938" s="1" t="s">
         <v>1532</v>
       </c>
@@ -75105,7 +75094,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="939" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B939" s="1" t="s">
         <v>1563</v>
       </c>
@@ -75174,7 +75163,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="940" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B940" s="1" t="s">
         <v>1569</v>
       </c>
@@ -75243,7 +75232,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="941" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B941" s="1" t="s">
         <v>1482</v>
       </c>
@@ -75312,7 +75301,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="942" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B942" s="1" t="s">
         <v>1507</v>
       </c>
@@ -75381,7 +75370,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="943" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B943" s="1" t="s">
         <v>1517</v>
       </c>
@@ -75450,7 +75439,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="944" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B944" s="1" t="s">
         <v>1537</v>
       </c>
@@ -75517,7 +75506,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="945" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B945" s="1" t="s">
         <v>1496</v>
       </c>
@@ -75586,7 +75575,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="946" spans="2:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B946" s="1" t="s">
         <v>1449</v>
       </c>
@@ -75662,14 +75651,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5a5f483f-f768-438e-b4ef-63f46a7558dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="dd8c73df-45bd-468c-aae5-f3faedcbd5e2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -75868,21 +75855,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5a5f483f-f768-438e-b4ef-63f46a7558dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="dd8c73df-45bd-468c-aae5-f3faedcbd5e2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB3953B9-FA70-4844-80DB-AA34ABB18FA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9374A74A-6917-4A7E-A58D-51B8613AA239}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5a5f483f-f768-438e-b4ef-63f46a7558dd"/>
-    <ds:schemaRef ds:uri="dd8c73df-45bd-468c-aae5-f3faedcbd5e2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -75907,9 +75893,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9374A74A-6917-4A7E-A58D-51B8613AA239}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB3953B9-FA70-4844-80DB-AA34ABB18FA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5a5f483f-f768-438e-b4ef-63f46a7558dd"/>
+    <ds:schemaRef ds:uri="dd8c73df-45bd-468c-aae5-f3faedcbd5e2"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>